--- a/Result/profitability/4915.xlsx
+++ b/Result/profitability/4915.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2675</v>
+        <v>1.2125</v>
       </c>
       <c r="N2" t="n">
-        <v>16.73625</v>
+        <v>16.455</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.66</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13875</v>
+        <v>1.165</v>
       </c>
       <c r="N3" t="n">
-        <v>16.39</v>
+        <v>16.0675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>1.02</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13625</v>
+        <v>1.09125</v>
       </c>
       <c r="N4" t="n">
-        <v>15.9375</v>
+        <v>15.645</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>1.16375</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>15.49</v>
+        <v>15.16375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.79</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1875</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>14.71375</v>
+        <v>14.44125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.14</v>
       </c>
       <c r="M7" t="n">
-        <v>1.26125</v>
+        <v>1.2975</v>
       </c>
       <c r="N7" t="n">
-        <v>13.96</v>
+        <v>13.615</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -9064,6 +9064,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4915</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>17212</v>
+      </c>
+      <c r="D69" t="n">
+        <v>14656</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2556</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="G69" t="n">
+        <v>644</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3.74%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>85</v>
+      </c>
+      <c r="J69" t="n">
+        <v>730</v>
+      </c>
+      <c r="K69" t="n">
+        <v>580</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N69" t="n">
+        <v>16.82125</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.03846153846153855</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>-1.050000000000001</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.0660377358490567</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-0.3500000000000001</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-0.21875</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-2.610000000000001</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-0.1494845360824743</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
